--- a/research/GMG.AX/Reports/GMG.AX_DCF_Model.xlsx
+++ b/research/GMG.AX/Reports/GMG.AX_DCF_Model.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="168">
   <si>
     <t xml:space="preserve">Ticker</t>
   </si>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Model</t>
   </si>
   <si>
-    <t xml:space="preserve">owner_fcf_dcf_component</t>
+    <t xml:space="preserve">REIT operating profit capitalisation at cost of equity (engine route; funds management plus IAS 40 co-investments)</t>
   </si>
   <si>
     <t xml:space="preserve">Currency (model)</t>
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Built at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-22T11:57:21Z</t>
+    <t xml:space="preserve">2026-09-22T20:11:25Z</t>
   </si>
   <si>
     <t xml:space="preserve">Drivers file</t>
@@ -218,6 +218,15 @@
   </si>
   <si>
     <t xml:space="preserve">Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AssetsUnderManagement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OperatingProfit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WeightedAvgSecurities</t>
   </si>
   <si>
     <t xml:space="preserve">FY2016</t>
@@ -1008,7 +1017,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1096,10 +1105,19 @@
       <c r="AB1" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="AC1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1714.3</v>
@@ -1155,10 +1173,16 @@
       <c r="AB2" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD2" s="0" t="n">
+        <v>715</v>
+      </c>
+      <c r="AE2" s="0" t="n">
+        <v>1770.3</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1650.5</v>
@@ -1214,10 +1238,16 @@
       <c r="AB3" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD3" s="0" t="n">
+        <v>776</v>
+      </c>
+      <c r="AE3" s="0" t="n">
+        <v>1787.3</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>1582.7</v>
@@ -1273,10 +1303,16 @@
       <c r="AB4" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD4" s="0" t="n">
+        <v>845.9</v>
+      </c>
+      <c r="AE4" s="0" t="n">
+        <v>1798.8</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>1718.6</v>
@@ -1332,10 +1368,16 @@
       <c r="AB5" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD5" s="0" t="n">
+        <v>942.3</v>
+      </c>
+      <c r="AE5" s="0" t="n">
+        <v>1811.7</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>1510.9</v>
@@ -1391,10 +1433,16 @@
       <c r="AB6" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD6" s="0" t="n">
+        <v>1060.2</v>
+      </c>
+      <c r="AE6" s="0" t="n">
+        <v>1826</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>1988.3</v>
@@ -1450,10 +1498,16 @@
       <c r="AB7" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD7" s="0" t="n">
+        <v>1219.4</v>
+      </c>
+      <c r="AE7" s="0" t="n">
+        <v>1844.2</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>2091.8</v>
@@ -1509,10 +1563,16 @@
       <c r="AB8" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD8" s="0" t="n">
+        <v>1528</v>
+      </c>
+      <c r="AE8" s="0" t="n">
+        <v>1863.7</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>1968.9</v>
@@ -1568,10 +1628,16 @@
       <c r="AB9" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD9" s="0" t="n">
+        <v>1783.2</v>
+      </c>
+      <c r="AE9" s="0" t="n">
+        <v>1878.6</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>1983.4</v>
@@ -1627,10 +1693,16 @@
       <c r="AB10" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD10" s="0" t="n">
+        <v>2049.4</v>
+      </c>
+      <c r="AE10" s="0" t="n">
+        <v>1896.7</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>2311</v>
@@ -1686,10 +1758,16 @@
       <c r="AB11" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD11" s="0" t="n">
+        <v>2311.2</v>
+      </c>
+      <c r="AE11" s="0" t="n">
+        <v>1950.9</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>2562.7</v>
@@ -1744,6 +1822,15 @@
       </c>
       <c r="AB12" s="0" t="s">
         <v>14</v>
+      </c>
+      <c r="AC12" s="0" t="n">
+        <v>75.4</v>
+      </c>
+      <c r="AD12" s="0" t="n">
+        <v>2674.5</v>
+      </c>
+      <c r="AE12" s="0" t="n">
+        <v>2042.6</v>
       </c>
     </row>
   </sheetData>
@@ -1770,15 +1857,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>26</v>
@@ -1786,7 +1873,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>2092.3</v>
@@ -1794,7 +1881,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
@@ -1802,7 +1889,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
@@ -1810,7 +1897,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>15</v>
@@ -1818,7 +1905,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>3204.4</v>
@@ -1826,23 +1913,23 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
@@ -1850,42 +1937,42 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>6</v>
@@ -1920,7 +2007,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>89.5</v>
@@ -1955,7 +2042,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>14.5</v>
@@ -1990,7 +2077,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
@@ -2025,7 +2112,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -2060,7 +2147,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>57.4</v>
@@ -2095,7 +2182,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>9</v>
@@ -2130,7 +2217,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>10</v>
@@ -2138,7 +2225,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>2.5</v>
@@ -2146,7 +2233,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>15</v>
@@ -2154,7 +2241,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>0</v>
@@ -2162,7 +2249,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>0.3</v>
@@ -2170,42 +2257,42 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>9</v>
@@ -2240,7 +2327,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>90</v>
@@ -2275,7 +2362,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>14.5</v>
@@ -2310,7 +2397,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>0</v>
@@ -2345,7 +2432,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>0</v>
@@ -2380,7 +2467,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>53.7</v>
@@ -2415,7 +2502,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>9</v>
@@ -2450,7 +2537,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>10</v>
@@ -2458,7 +2545,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>3</v>
@@ -2466,7 +2553,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>18</v>
@@ -2474,7 +2561,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>0</v>
@@ -2482,7 +2569,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>0.5</v>
@@ -2490,42 +2577,42 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>10</v>
@@ -2560,7 +2647,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>90.5</v>
@@ -2595,7 +2682,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>14.5</v>
@@ -2630,7 +2717,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -2665,7 +2752,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -2700,7 +2787,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>56</v>
@@ -2735,7 +2822,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>9</v>
@@ -2770,7 +2857,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B48" s="3" t="n">
         <v>10</v>
@@ -2778,7 +2865,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B49" s="3" t="n">
         <v>3.5</v>
@@ -2786,7 +2873,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B50" s="3" t="n">
         <v>20</v>
@@ -2794,7 +2881,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B51" s="3" t="n">
         <v>0</v>
@@ -2802,7 +2889,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B52" s="3" t="n">
         <v>0.2</v>
@@ -2832,50 +2919,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>0</v>
@@ -2923,7 +3010,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">Assumptions!C13</f>
@@ -3016,7 +3103,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">Assumptions!C14</f>
@@ -3106,7 +3193,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C9" s="4" t="n">
         <f aca="false">Assumptions!C15</f>
@@ -3151,7 +3238,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">-C6*C9/100</f>
@@ -3196,7 +3283,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">C8+C10+C24</f>
@@ -3241,7 +3328,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">-C6*Assumptions!C17/100</f>
@@ -3286,7 +3373,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">C11+C12</f>
@@ -3331,7 +3418,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C14" s="4" t="n">
         <f aca="false">Assumptions!C19</f>
@@ -3376,7 +3463,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C15" s="0" t="n">
         <f aca="false">C13-MAX(0,C13)*C14/100</f>
@@ -3421,7 +3508,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">-C12</f>
@@ -3466,7 +3553,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C17" s="4" t="n">
         <f aca="false">-C6*Assumptions!C18/100</f>
@@ -3511,7 +3598,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C18" s="4" t="n">
         <f aca="false">(C6-B6)*Assumptions!$B$23/100</f>
@@ -3556,7 +3643,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C19" s="0" t="n">
         <f aca="false">C15+C16+C17+C18</f>
@@ -3601,7 +3688,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C20" s="0" t="n">
         <f aca="false">1/(1+$B$27/100)^C4</f>
@@ -3646,7 +3733,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C21" s="0" t="n">
         <f aca="false">C19*C20</f>
@@ -3691,7 +3778,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C23" s="4" t="n">
         <f aca="false">Assumptions!C16</f>
@@ -3736,7 +3823,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">-C6*C23/100</f>
@@ -3781,12 +3868,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B27" s="4" t="n">
         <f aca="false">Assumptions!$B$20</f>
@@ -3795,7 +3882,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B28" s="4" t="n">
         <f aca="false">Assumptions!$B$21</f>
@@ -3804,7 +3891,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B29" s="4" t="n">
         <f aca="false">Assumptions!$B$22</f>
@@ -3813,7 +3900,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">SUM(C21:L21)</f>
@@ -3822,7 +3909,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B31" s="0" t="n">
         <f aca="false">L19</f>
@@ -3831,7 +3918,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,B31*(1+B28/100)/((B27-B28)/100),B31*B29)</f>
@@ -3840,7 +3927,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">B31*B29</f>
@@ -3849,7 +3936,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">MAX(0,MIN(B32,B33))</f>
@@ -3858,7 +3945,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">B34/(1+B27/100)^L4</f>
@@ -3867,7 +3954,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">B30+B35</f>
@@ -3876,7 +3963,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B37" s="0" t="n">
         <f aca="false">B36+Assumptions!$B$5-Assumptions!$B$4</f>
@@ -3885,7 +3972,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B38" s="0" t="n">
         <f aca="false">B37/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -3894,7 +3981,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B39" s="4" t="n">
         <f aca="false">B38/Assumptions!$B$2-1</f>
@@ -3903,7 +3990,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B41" s="0" t="n">
         <f aca="false">SUMPRODUCT(-C10:L10/(1+$B$27/100)^C4:L4)</f>
@@ -3912,7 +3999,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B42" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,-L10*(1+B28/100)/((B27-B28)/100),-L10*20)/(1+B27/100)^L4</f>
@@ -3921,7 +4008,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B43" s="0" t="n">
         <f aca="false">(B37+B41+B42)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -3930,7 +4017,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B45" s="4" t="n">
         <f aca="false">Assumptions!$B$6</f>
@@ -3939,7 +4026,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B46" s="0" t="n">
         <f aca="false">MAX(0,MIN(IF(B45&gt;B28,B31*(1+B28/100)/((B45-B28)/100),B31*B29),B31*B29))</f>
@@ -3948,7 +4035,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B47" s="0" t="n">
         <f aca="false">(SUMPRODUCT(C19:L19/(1+B45/100)^C4:L4)+B46/(1+B45/100)^L4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -3979,50 +4066,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>0</v>
@@ -4070,7 +4157,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">Assumptions!C27</f>
@@ -4163,7 +4250,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">Assumptions!C28</f>
@@ -4253,7 +4340,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C9" s="4" t="n">
         <f aca="false">Assumptions!C29</f>
@@ -4298,7 +4385,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">-C6*C9/100</f>
@@ -4343,7 +4430,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">C8+C10+C24</f>
@@ -4388,7 +4475,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">-C6*Assumptions!C31/100</f>
@@ -4433,7 +4520,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">C11+C12</f>
@@ -4478,7 +4565,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C14" s="4" t="n">
         <f aca="false">Assumptions!C33</f>
@@ -4523,7 +4610,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C15" s="0" t="n">
         <f aca="false">C13-MAX(0,C13)*C14/100</f>
@@ -4568,7 +4655,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">-C12</f>
@@ -4613,7 +4700,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C17" s="4" t="n">
         <f aca="false">-C6*Assumptions!C32/100</f>
@@ -4658,7 +4745,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C18" s="4" t="n">
         <f aca="false">(C6-B6)*Assumptions!$B$37/100</f>
@@ -4703,7 +4790,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C19" s="0" t="n">
         <f aca="false">C15+C16+C17+C18</f>
@@ -4748,7 +4835,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C20" s="0" t="n">
         <f aca="false">1/(1+$B$27/100)^C4</f>
@@ -4793,7 +4880,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C21" s="0" t="n">
         <f aca="false">C19*C20</f>
@@ -4838,7 +4925,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C23" s="4" t="n">
         <f aca="false">Assumptions!C30</f>
@@ -4883,7 +4970,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">-C6*C23/100</f>
@@ -4928,12 +5015,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B27" s="4" t="n">
         <f aca="false">Assumptions!$B$34</f>
@@ -4942,7 +5029,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B28" s="4" t="n">
         <f aca="false">Assumptions!$B$35</f>
@@ -4951,7 +5038,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B29" s="4" t="n">
         <f aca="false">Assumptions!$B$36</f>
@@ -4960,7 +5047,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">SUM(C21:L21)</f>
@@ -4969,7 +5056,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B31" s="0" t="n">
         <f aca="false">L19</f>
@@ -4978,7 +5065,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,B31*(1+B28/100)/((B27-B28)/100),B31*B29)</f>
@@ -4987,7 +5074,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">B31*B29</f>
@@ -4996,7 +5083,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">MAX(0,MIN(B32,B33))</f>
@@ -5005,7 +5092,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">B34/(1+B27/100)^L4</f>
@@ -5014,7 +5101,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">B30+B35</f>
@@ -5023,7 +5110,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B37" s="0" t="n">
         <f aca="false">B36+Assumptions!$B$5-Assumptions!$B$4</f>
@@ -5032,7 +5119,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B38" s="0" t="n">
         <f aca="false">B37/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -5041,7 +5128,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B39" s="4" t="n">
         <f aca="false">B38/Assumptions!$B$2-1</f>
@@ -5050,7 +5137,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B41" s="0" t="n">
         <f aca="false">SUMPRODUCT(-C10:L10/(1+$B$27/100)^C4:L4)</f>
@@ -5059,7 +5146,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B42" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,-L10*(1+B28/100)/((B27-B28)/100),-L10*20)/(1+B27/100)^L4</f>
@@ -5068,7 +5155,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B43" s="0" t="n">
         <f aca="false">(B37+B41+B42)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -5077,7 +5164,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B45" s="4" t="n">
         <f aca="false">Assumptions!$B$6</f>
@@ -5086,7 +5173,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B46" s="0" t="n">
         <f aca="false">MAX(0,MIN(IF(B45&gt;B28,B31*(1+B28/100)/((B45-B28)/100),B31*B29),B31*B29))</f>
@@ -5095,7 +5182,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B47" s="0" t="n">
         <f aca="false">(SUMPRODUCT(C19:L19/(1+B45/100)^C4:L4)+B46/(1+B45/100)^L4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -5126,50 +5213,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>0</v>
@@ -5217,7 +5304,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">Assumptions!C41</f>
@@ -5310,7 +5397,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">Assumptions!C42</f>
@@ -5400,7 +5487,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C9" s="4" t="n">
         <f aca="false">Assumptions!C43</f>
@@ -5445,7 +5532,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">-C6*C9/100</f>
@@ -5490,7 +5577,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">C8+C10+C24</f>
@@ -5535,7 +5622,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">-C6*Assumptions!C45/100</f>
@@ -5580,7 +5667,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">C11+C12</f>
@@ -5625,7 +5712,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C14" s="4" t="n">
         <f aca="false">Assumptions!C47</f>
@@ -5670,7 +5757,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C15" s="0" t="n">
         <f aca="false">C13-MAX(0,C13)*C14/100</f>
@@ -5715,7 +5802,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">-C12</f>
@@ -5760,7 +5847,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C17" s="4" t="n">
         <f aca="false">-C6*Assumptions!C46/100</f>
@@ -5805,7 +5892,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C18" s="4" t="n">
         <f aca="false">(C6-B6)*Assumptions!$B$51/100</f>
@@ -5850,7 +5937,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C19" s="0" t="n">
         <f aca="false">C15+C16+C17+C18</f>
@@ -5895,7 +5982,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C20" s="0" t="n">
         <f aca="false">1/(1+$B$27/100)^C4</f>
@@ -5940,7 +6027,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C21" s="0" t="n">
         <f aca="false">C19*C20</f>
@@ -5985,7 +6072,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C23" s="4" t="n">
         <f aca="false">Assumptions!C44</f>
@@ -6030,7 +6117,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">-C6*C23/100</f>
@@ -6075,12 +6162,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B27" s="4" t="n">
         <f aca="false">Assumptions!$B$48</f>
@@ -6089,7 +6176,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B28" s="4" t="n">
         <f aca="false">Assumptions!$B$49</f>
@@ -6098,7 +6185,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B29" s="4" t="n">
         <f aca="false">Assumptions!$B$50</f>
@@ -6107,7 +6194,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">SUM(C21:L21)</f>
@@ -6116,7 +6203,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B31" s="0" t="n">
         <f aca="false">L19</f>
@@ -6125,7 +6212,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,B31*(1+B28/100)/((B27-B28)/100),B31*B29)</f>
@@ -6134,7 +6221,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">B31*B29</f>
@@ -6143,7 +6230,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">MAX(0,MIN(B32,B33))</f>
@@ -6152,7 +6239,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">B34/(1+B27/100)^L4</f>
@@ -6161,7 +6248,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">B30+B35</f>
@@ -6170,7 +6257,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B37" s="0" t="n">
         <f aca="false">B36+Assumptions!$B$5-Assumptions!$B$4</f>
@@ -6179,7 +6266,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B38" s="0" t="n">
         <f aca="false">B37/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6188,7 +6275,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B39" s="4" t="n">
         <f aca="false">B38/Assumptions!$B$2-1</f>
@@ -6197,7 +6284,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B41" s="0" t="n">
         <f aca="false">SUMPRODUCT(-C10:L10/(1+$B$27/100)^C4:L4)</f>
@@ -6206,7 +6293,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B42" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,-L10*(1+B28/100)/((B27-B28)/100),-L10*20)/(1+B27/100)^L4</f>
@@ -6215,7 +6302,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B43" s="0" t="n">
         <f aca="false">(B37+B41+B42)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6224,7 +6311,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B45" s="4" t="n">
         <f aca="false">Assumptions!$B$6</f>
@@ -6233,7 +6320,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B46" s="0" t="n">
         <f aca="false">MAX(0,MIN(IF(B45&gt;B28,B31*(1+B28/100)/((B45-B28)/100),B31*B29),B31*B29))</f>
@@ -6242,7 +6329,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B47" s="0" t="n">
         <f aca="false">(SUMPRODUCT(C19:L19/(1+B45/100)^C4:L4)+B46/(1+B45/100)^L4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6273,32 +6360,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B4" s="4" t="n">
         <f aca="false">DCF_Bear!$B$38</f>
@@ -6323,7 +6410,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B5" s="4" t="n">
         <f aca="false">DCF_Base!$B$38</f>
@@ -6348,7 +6435,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B6" s="4" t="n">
         <f aca="false">DCF_Bull!$B$38</f>
@@ -6373,7 +6460,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">SUMPRODUCT(B4:B6,D4:D6)</f>
@@ -6382,7 +6469,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">SUMPRODUCT(E4:E6,D4:D6)</f>
@@ -6391,7 +6478,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">1-Assumptions!$B$2/B8</f>
@@ -6400,7 +6487,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">IF(ABS(B9-B8)&gt;0.01*ABS(B8),(Assumptions!$B$2-B8)/(B9-B8)*100,"n/a")</f>
@@ -6409,7 +6496,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">SUMPRODUCT(F4:F6,D4:D6)</f>
@@ -6418,15 +6505,15 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$15/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$15&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$15-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$15/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6438,7 +6525,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B16" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$16/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$16&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$16-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$16/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6450,7 +6537,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$17/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$17&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$17-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$17/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6462,7 +6549,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$18/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$18&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$18-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$18/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6474,7 +6561,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$19/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$19&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$19-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$19/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6486,7 +6573,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
